--- a/astro-site/public/dl/kit-tareas-pasteleria/08-apertura-cierre-negocio.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/08-apertura-cierre-negocio.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Apertura del Negocio" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cierre del Negocio" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura del Negocio" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre del Negocio" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="0" name="_xlnm.Print_Area">'Instrucciones'!$A$1:$A$20</definedName>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Apertura del Negocio'!$A$1:$H$24</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Cierre del Negocio'!$A$1:$H$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$A$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura del Negocio'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura del Negocio'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cierre del Negocio'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre del Negocio'!$A$1:$H$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,6 +77,11 @@
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00888888"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00999999"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -140,51 +147,52 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -546,120 +554,128 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="80"/>
+    <col width="80" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="40" r="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>AI Chef Pro — aichef.pro</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="30" r="2">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Kit de Tareas — Pastelería / Obrador</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="25" r="3">
+    <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Checklist de Apertura y Cierre del Negocio</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="35" r="5">
+    <row r="4"/>
+    <row r="5" ht="35" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>📋 Instrucciones de Uso</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>1. Este archivo contiene checklists profesionales para la apertura y cierre de tu negocio.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2. Imprime las hojas que necesites o úsalas en formato digital (tablet/ordenador).</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>3. Cada checklist incluye columnas para marcar tareas completadas, responsable, hora y notas.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>4. Personaliza las tareas según las necesidades específicas de tu establecimiento.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="10">
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>5. Añade o elimina filas según tu operativa diaria.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="11">
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>6. Usa la validación de datos en la columna '✓ Completada' para marcar el estado.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="12">
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>7. Rellena la firma y fecha cada día para mantener el control.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="13">
+    <row r="13" ht="22" customHeight="1">
       <c r="A13" s="5" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="14">
+    <row r="14" ht="22" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>💡 Consejo: Plastifica una copia impresa y usa rotuladores borrables para reutilizarla cada día.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="15">
+    <row r="15" ht="22" customHeight="1">
       <c r="A15" s="5" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="16">
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>© AI Chef Pro — aichef.pro</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="17">
+    <row r="17" ht="22" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>29 años de experiencia en alta hostelería · 15 años de consultoría gastronómica</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="22" r="18">
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -667,7 +683,8 @@
   <mergeCells count="1">
     <mergeCell ref="A1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -676,29 +693,29 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="50"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="13"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="25"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="40" r="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Apertura del Negocio — Pastelería / Obrador</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="28" r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Fecha: ____/____/________</t>
@@ -710,8 +727,8 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="8" r="3"/>
-    <row customHeight="1" ht="28" r="4">
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>#</t>
@@ -753,7 +770,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="24" r="5">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
@@ -773,7 +790,7 @@
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="6">
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="10" t="n">
         <v>2</v>
       </c>
@@ -793,7 +810,7 @@
       <c r="G6" s="10" t="inlineStr"/>
       <c r="H6" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="7">
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="8" t="n">
         <v>3</v>
       </c>
@@ -813,7 +830,7 @@
       <c r="G7" s="8" t="inlineStr"/>
       <c r="H7" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="8">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
@@ -833,7 +850,7 @@
       <c r="G8" s="10" t="inlineStr"/>
       <c r="H8" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="9">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="8" t="n">
         <v>5</v>
       </c>
@@ -853,7 +870,7 @@
       <c r="G9" s="8" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="10">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="10" t="n">
         <v>6</v>
       </c>
@@ -873,7 +890,7 @@
       <c r="G10" s="10" t="inlineStr"/>
       <c r="H10" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="11">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
@@ -893,7 +910,7 @@
       <c r="G11" s="8" t="inlineStr"/>
       <c r="H11" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="12">
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="10" t="n">
         <v>8</v>
       </c>
@@ -913,7 +930,7 @@
       <c r="G12" s="10" t="inlineStr"/>
       <c r="H12" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="13">
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="8" t="n">
         <v>9</v>
       </c>
@@ -933,7 +950,7 @@
       <c r="G13" s="8" t="inlineStr"/>
       <c r="H13" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="14">
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
@@ -953,7 +970,7 @@
       <c r="G14" s="10" t="inlineStr"/>
       <c r="H14" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="15">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="8" t="n">
         <v>11</v>
       </c>
@@ -973,7 +990,7 @@
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="16">
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="10" t="n">
         <v>12</v>
       </c>
@@ -993,7 +1010,7 @@
       <c r="G16" s="10" t="inlineStr"/>
       <c r="H16" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="17">
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="8" t="n">
         <v>13</v>
       </c>
@@ -1013,7 +1030,7 @@
       <c r="G17" s="8" t="inlineStr"/>
       <c r="H17" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="18">
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="10" t="n">
         <v>14</v>
       </c>
@@ -1033,7 +1050,7 @@
       <c r="G18" s="10" t="inlineStr"/>
       <c r="H18" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="19">
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" s="8" t="n">
         <v>15</v>
       </c>
@@ -1053,7 +1070,7 @@
       <c r="G19" s="8" t="inlineStr"/>
       <c r="H19" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="20">
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="10" t="n">
         <v>16</v>
       </c>
@@ -1073,7 +1090,7 @@
       <c r="G20" s="10" t="inlineStr"/>
       <c r="H20" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="21">
+    <row r="21" ht="24" customHeight="1">
       <c r="A21" s="8" t="n">
         <v>17</v>
       </c>
@@ -1093,7 +1110,8 @@
       <c r="G21" s="8" t="inlineStr"/>
       <c r="H21" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="30" r="23">
+    <row r="22"/>
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Firma del responsable: _________________________     Hora de finalización: ________</t>
@@ -1116,12 +1134,20 @@
     <mergeCell ref="A23:H23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Selecciona ✓, ✗ o —" errorTitle="Valor no válido" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Selecciona ✓, ✗ o —" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1130,29 +1156,29 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="50"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="13"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="25"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="40" r="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cierre del Negocio — Pastelería / Obrador</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="28" r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Fecha: ____/____/________</t>
@@ -1164,8 +1190,8 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="8" r="3"/>
-    <row customHeight="1" ht="28" r="4">
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>#</t>
@@ -1207,7 +1233,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="24" r="5">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
@@ -1227,7 +1253,7 @@
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="6">
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="10" t="n">
         <v>2</v>
       </c>
@@ -1247,7 +1273,7 @@
       <c r="G6" s="10" t="inlineStr"/>
       <c r="H6" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="7">
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="8" t="n">
         <v>3</v>
       </c>
@@ -1267,7 +1293,7 @@
       <c r="G7" s="8" t="inlineStr"/>
       <c r="H7" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="8">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
@@ -1287,7 +1313,7 @@
       <c r="G8" s="10" t="inlineStr"/>
       <c r="H8" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="9">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="8" t="n">
         <v>5</v>
       </c>
@@ -1307,7 +1333,7 @@
       <c r="G9" s="8" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="10">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="10" t="n">
         <v>6</v>
       </c>
@@ -1327,7 +1353,7 @@
       <c r="G10" s="10" t="inlineStr"/>
       <c r="H10" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="11">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
@@ -1347,7 +1373,7 @@
       <c r="G11" s="8" t="inlineStr"/>
       <c r="H11" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="12">
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="10" t="n">
         <v>8</v>
       </c>
@@ -1367,7 +1393,7 @@
       <c r="G12" s="10" t="inlineStr"/>
       <c r="H12" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="13">
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="8" t="n">
         <v>9</v>
       </c>
@@ -1387,7 +1413,7 @@
       <c r="G13" s="8" t="inlineStr"/>
       <c r="H13" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="14">
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
@@ -1407,7 +1433,7 @@
       <c r="G14" s="10" t="inlineStr"/>
       <c r="H14" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="15">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="8" t="n">
         <v>11</v>
       </c>
@@ -1427,7 +1453,7 @@
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="16">
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="10" t="n">
         <v>12</v>
       </c>
@@ -1447,7 +1473,7 @@
       <c r="G16" s="10" t="inlineStr"/>
       <c r="H16" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="17">
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="8" t="n">
         <v>13</v>
       </c>
@@ -1467,7 +1493,7 @@
       <c r="G17" s="8" t="inlineStr"/>
       <c r="H17" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="18">
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="10" t="n">
         <v>14</v>
       </c>
@@ -1487,7 +1513,7 @@
       <c r="G18" s="10" t="inlineStr"/>
       <c r="H18" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="19">
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" s="8" t="n">
         <v>15</v>
       </c>
@@ -1507,7 +1533,8 @@
       <c r="G19" s="8" t="inlineStr"/>
       <c r="H19" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="30" r="21">
+    <row r="20"/>
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Firma del responsable: _________________________     Hora de finalización: ________</t>
@@ -1530,11 +1557,19 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Selecciona ✓, ✗ o —" errorTitle="Valor no válido" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19" type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Selecciona ✓, ✗ o —" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-pasteleria/08-apertura-cierre-negocio.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/08-apertura-cierre-negocio.xlsx
@@ -717,7 +717,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>▸ La primera tarea del día son las vitrinas: enciéndelas mínimo 45 minutos antes de montar el género, que es lo que tardan en bajar a 2-6 °C. El cronograma las enciende a las 06:45, monta a las 07:45 y abre al público a las 08:00.</t>
+          <t>▸ La primera tarea del día son las vitrinas: enciéndelas mínimo 45 minutos antes de montar el género, que es lo que tardan en bajar a 0-4 °C — el tope que el RD 1021/2022 (art. 4.1, fila 9) fija al producto de pastelería relleno. El cronograma las enciende a las 06:45, monta a las 07:45 y abre al público a las 08:00.</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
     <row r="25">
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+          <t>Versión 2.1 · septiembre 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Desactivar la alarma y encender las vitrinas refrigeradas: anotar la temperatura (2-6 °C) — mínimo 45 minutos antes de montar el género (→ 13 Registro de Temperaturas · hoja Registro de Temperaturas)</t>
+          <t>Desactivar la alarma y encender las vitrinas refrigeradas: anotar la temperatura (0-4 °C) — mínimo 45 minutos antes de montar el género (→ 13 Registro de Temperaturas · hoja Registro de Temperaturas)</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Comprobar que las vitrinas han bajado a 2-6 °C antes de montar; si no han llegado, retrasar el montaje</t>
+          <t>Comprobar que las vitrinas han bajado a 0-4 °C antes de montar; si no han llegado, retrasar el montaje</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
